--- a/source_code/input_files/input_file_template/template_conductor_1_input.xlsx
+++ b/source_code/input_files/input_file_template/template_conductor_1_input.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAN" sheetId="2" r:id="Re14111f267b94d8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STACK" sheetId="5" r:id="R80d8dee6837a4516"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_MIX" sheetId="3" r:id="Rc08c2d95e7ee4081"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_STAB" sheetId="6" r:id="Rf4fe3c9237914be5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_JACKET" sheetId="4" r:id="R1f86d09aa7e74255"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAN" sheetId="2" r:id="R2502da473a0d4381"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STACK" sheetId="5" r:id="Rd8d39bf58e2f4e80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_MIX" sheetId="3" r:id="Re88592fac6ff492c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_STAB" sheetId="6" r:id="R68b706c4316442dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_JACKET" sheetId="4" r:id="Re3c02a87c5364c59"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -38,15 +38,9 @@
     <x:t xml:space="preserve">m</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">x coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Y_barycenter</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">y coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">FLUID_TYPE</x:t>
   </x:si>
   <x:si>
@@ -80,9 +74,6 @@
     <x:t xml:space="preserve">VOID_FRACTION</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">VIOD FRACTION OF THE CHANNEL = VOID AREA/TOTALAREA OF THE CHANNEL</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">IFRICTION</x:t>
   </x:si>
   <x:si>
@@ -135,9 +126,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">element of the type "SC+Cu strands"</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">row used to get the correct number of mixed copper-supeconductor strands objects in cell B1 as the sum of values in this row starting from cell D2</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">element of the type "Cu strands"</x:t>
@@ -784,8 +772,8 @@
       <x:c r="C5" s="44" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D5" s="48" t="s">
-        <x:v>8</x:v>
+      <x:c r="D5" s="48" t="str">
+        <x:v>x coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E5" s="45" t="n">
         <x:v>0</x:v>
@@ -796,7 +784,7 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="43" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="44" t="s">
         <x:v>7</x:v>
@@ -804,8 +792,8 @@
       <x:c r="C6" s="44" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D6" s="48" t="s">
-        <x:v>10</x:v>
+      <x:c r="D6" s="48" t="str">
+        <x:v>y coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E6" s="45" t="n">
         <x:v>0</x:v>
@@ -816,16 +804,16 @@
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="43" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B7" s="44" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C7" s="44" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B7" s="44" t="s">
+      <x:c r="D7" s="48" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="44" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D7" s="48" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="E7" s="44" t="str">
         <x:v>Helium</x:v>
@@ -836,7 +824,7 @@
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="43" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B8" s="44" t="s">
         <x:v>7</x:v>
@@ -845,7 +833,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D8" s="48" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E8" s="46" t="n">
         <x:v>0.008</x:v>
@@ -856,7 +844,7 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="43" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="44" t="s">
         <x:v>7</x:v>
@@ -865,7 +853,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D9" s="48" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="46" t="n">
         <x:v>0</x:v>
@@ -876,16 +864,16 @@
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="43" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B10" s="44" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C10" s="44" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D10" s="48" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E10" s="44" t="n">
         <x:v>1</x:v>
@@ -896,16 +884,16 @@
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="43" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B11" s="44" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C11" s="44" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D11" s="48" t="s">
-        <x:v>22</x:v>
+      <x:c r="D11" s="48" t="str">
+        <x:v>VOID FRACTION OF THE CHANNEL = VOID AREA / TOTAL AREA OF THE CHANNEL</x:v>
       </x:c>
       <x:c r="E11" s="44" t="n">
         <x:v>1</x:v>
@@ -916,16 +904,16 @@
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="43" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B12" s="44" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C12" s="44" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D12" s="48" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E12" s="44" t="n">
         <x:v>-99</x:v>
@@ -936,16 +924,16 @@
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="43" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B13" s="44" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C13" s="44" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D13" s="48" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E13" s="44" t="n">
         <x:v>0.02</x:v>
@@ -956,13 +944,13 @@
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="43" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B14" s="44" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C14" s="44" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D14" s="48"/>
       <x:c r="E14" s="63" t="b">
@@ -974,7 +962,7 @@
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="43" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B15" s="44" t="s">
         <x:v>7</x:v>
@@ -992,7 +980,7 @@
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="43" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B16" s="44" t="s">
         <x:v>7</x:v>
@@ -1010,16 +998,16 @@
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="43" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B17" s="44" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C17" s="44" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D17" s="48" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E17" s="44" t="str">
         <x:v>hole</x:v>
@@ -1030,16 +1018,16 @@
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="43" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B18" s="44" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C18" s="44" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D18" s="48" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E18" s="44" t="n">
         <x:v>1</x:v>
@@ -1050,16 +1038,16 @@
     </x:row>
     <x:row r="19" ht="24" hidden="0" customHeight="1">
       <x:c r="A19" s="43" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B19" s="44" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C19" s="44" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D19" s="48" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E19" s="63" t="b">
         <x:v>0</x:v>
@@ -1095,7 +1083,7 @@
       </x:c>
       <x:c r="C1" s="41"/>
       <x:c r="D1" s="47" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E1" s="41" t="n">
         <x:v>0</x:v>
@@ -1106,7 +1094,7 @@
       <x:c r="B2" s="34"/>
       <x:c r="C2" s="34"/>
       <x:c r="D2" s="36" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E2" s="32" t="n">
         <x:f>IF(E$1&gt;0,1,0)</x:f>
@@ -1600,7 +1588,7 @@
       </x:c>
       <x:c r="C1" s="41"/>
       <x:c r="D1" s="47" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E1" s="41" t="n">
         <x:v>1</x:v>
@@ -1610,8 +1598,8 @@
       <x:c r="A2" s="35"/>
       <x:c r="B2" s="34"/>
       <x:c r="C2" s="34"/>
-      <x:c r="D2" s="36" t="s">
-        <x:v>41</x:v>
+      <x:c r="D2" s="36" t="str">
+        <x:v>Row used to determine the number of mixed copper-superconductor strand objects in cell B1, calculated as the sum of the values in this row starting from cell D2.</x:v>
       </x:c>
       <x:c r="E2" s="32" t="n">
         <x:f>IF(E$1&gt;0,1,0)</x:f>
@@ -2020,7 +2008,7 @@
       </x:c>
       <x:c r="C1" s="41"/>
       <x:c r="D1" s="47" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E1" s="41" t="n">
         <x:v>0</x:v>
@@ -2031,7 +2019,7 @@
       <x:c r="B2" s="34"/>
       <x:c r="C2" s="34"/>
       <x:c r="D2" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E2" s="32" t="n">
         <x:f>IF(E$1&gt;0,1,0)</x:f>
@@ -2084,7 +2072,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D5" s="48" t="str">
-        <x:v>x coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>x coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E5" s="45" t="n">
         <x:v>0</x:v>
@@ -2101,7 +2089,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D6" s="48" t="str">
-        <x:v>y coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>y coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E6" s="45" t="n">
         <x:v>0</x:v>
@@ -2202,7 +2190,7 @@
       </x:c>
       <x:c r="C1" s="41"/>
       <x:c r="D1" s="47" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E1" s="41" t="n">
         <x:v>1</x:v>
@@ -2213,7 +2201,7 @@
       <x:c r="B2" s="34"/>
       <x:c r="C2" s="34"/>
       <x:c r="D2" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E2" s="32" t="n">
         <x:f>IF(E$1&gt;0,1,0)</x:f>
@@ -2283,7 +2271,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D6" s="48" t="str">
-        <x:v>x coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>x coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E6" s="45" t="n">
         <x:v>0</x:v>
@@ -2300,7 +2288,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D7" s="48" t="str">
-        <x:v>y coordinate of the barycenter Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>y coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E7" s="45" t="n">
         <x:v>0</x:v>
